--- a/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>518 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.564071</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.26791</v>
-      </c>
-      <c r="I2" t="n">
-        <v>211</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.564071</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.26791</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>85 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.566944</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.27055900000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>460</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.566944</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.270559</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>20394 JORGE ORTIZ DUEÑAS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.580878</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.268669</v>
-      </c>
-      <c r="I4" t="n">
-        <v>255</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.580878</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.268669</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>20395 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.521612</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.248215</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>64</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.521612</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.248215</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.501327</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.29513799999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>854</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.501327</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.295138</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>20390 HORTENCIA DULANTO DE LAS CASAS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.56764</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.271648</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1437</v>
-      </c>
-      <c r="J7" t="n">
-        <v>58</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.56764</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.271648</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>20799 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.490346</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.304839</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1159</v>
-      </c>
-      <c r="J8" t="n">
-        <v>73</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.490346</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.304839</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>20392 JUAN PASCUAL PRINGLES</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.588432</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.260829</v>
-      </c>
-      <c r="I9" t="n">
-        <v>921</v>
-      </c>
-      <c r="J9" t="n">
-        <v>51</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.588432</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.260829</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>CET 34</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.560798</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.268857</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1603</v>
-      </c>
-      <c r="J10" t="n">
-        <v>106</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.560798</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.268857</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.558853</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.273156</v>
-      </c>
-      <c r="I11" t="n">
-        <v>601</v>
-      </c>
-      <c r="J11" t="n">
-        <v>37</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.558853</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.273156</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.567256</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.27104300000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>887</v>
-      </c>
-      <c r="J12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.567256</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.271043</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>20393 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.50942</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.290471</v>
-      </c>
-      <c r="I13" t="n">
-        <v>941</v>
-      </c>
-      <c r="J13" t="n">
-        <v>44</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.50942</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.290471</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>20391 JORGE BRAVO DE RUEDA QUEROL</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.559115</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.272031</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1091</v>
-      </c>
-      <c r="J14" t="n">
-        <v>45</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.559115</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.272031</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.568961</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.27068</v>
-      </c>
-      <c r="I15" t="n">
-        <v>320</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.568961</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.27068</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>VICENTE HONDARZA GOMEZ</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.564219</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.271073</v>
-      </c>
-      <c r="I16" t="n">
-        <v>396</v>
-      </c>
-      <c r="J16" t="n">
-        <v>30</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.564219</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.271073</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>EL MUNDO DE LOS NIÑOS - MUNDO SCHOOL E.I.R.L.</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.558917</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.27072800000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>249</v>
-      </c>
-      <c r="J17" t="n">
-        <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.558917</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.270728</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SEÑOR DE LA SOLEDAD</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.579748</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.260341</v>
-      </c>
-      <c r="I18" t="n">
-        <v>252</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.579748</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.260341</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>PEQUEÑA BELEN</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.588477</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.259665</v>
-      </c>
-      <c r="I19" t="n">
-        <v>493</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.588477</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.259665</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>SAN MARCOS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.559436</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.26912</v>
-      </c>
-      <c r="I20" t="n">
-        <v>357</v>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.559436</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.26912</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>SANTO DOMINGO DE CHANCAY</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.5647</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.27388000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>362</v>
-      </c>
-      <c r="J21" t="n">
-        <v>23</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.5647</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.27388</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>355779</t>
+          <t>355963</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>518 SEÑOR DE LOS MILAGROS</t>
+          <t>CET 34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.564071</t>
+          <t>-11.560798</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.26791</t>
+          <t>-77.268857</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>355802</t>
+          <t>783332</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85 MARIA INMACULADA CONCEPCION</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.566944</t>
+          <t>-11.559436</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.270559</t>
+          <t>-77.26912</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>355864</t>
+          <t>566098</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20395 NUESTRA SEÑORA DE FATIMA</t>
+          <t>SEÑOR DE LA SOLEDAD</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.521612</t>
+          <t>-11.579748</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.248215</t>
+          <t>-77.260341</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>355878</t>
+          <t>356024</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA CANDELARIA</t>
+          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.501327</t>
+          <t>-11.568961</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.295138</t>
+          <t>-77.27068</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>355920</t>
+          <t>734110</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20390 HORTENCIA DULANTO DE LAS CASAS</t>
+          <t>PEQUEÑA BELEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.56764</t>
+          <t>-11.588477</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.271648</t>
+          <t>-77.259665</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>493</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>355944</t>
+          <t>863055</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20799 DANIEL ALCIDES CARRION</t>
+          <t>SANTO DOMINGO DE CHANCAY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.490346</t>
+          <t>-11.5647</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.304839</t>
+          <t>-77.27388</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>355958</t>
+          <t>355802</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20392 JUAN PASCUAL PRINGLES</t>
+          <t>85 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.588432</t>
+          <t>-11.566944</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.260829</t>
+          <t>-77.270559</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>355963</t>
+          <t>356137</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CET 34</t>
+          <t>EL MUNDO DE LOS NIÑOS - MUNDO SCHOOL E.I.R.L.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.560798</t>
+          <t>-11.558917</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.268857</t>
+          <t>-77.270728</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>356081</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>VICENTE HONDARZA GOMEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.558853</t>
+          <t>-11.564219</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.273156</t>
+          <t>-77.271073</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>355982</t>
+          <t>355977</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.567256</t>
+          <t>-11.558853</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.271043</t>
+          <t>-77.273156</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>601</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>356000</t>
+          <t>355982</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20393 TUPAC AMARU</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.50942</t>
+          <t>-11.567256</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.290471</t>
+          <t>-77.271043</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>356019</t>
+          <t>355878</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20391 JORGE BRAVO DE RUEDA QUEROL</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.559115</t>
+          <t>-11.501327</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.272031</t>
+          <t>-77.295138</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>854</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>356024</t>
+          <t>356000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
+          <t>20393 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.568961</t>
+          <t>-11.50942</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.27068</t>
+          <t>-77.290471</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>941</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>356081</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VICENTE HONDARZA GOMEZ</t>
+          <t>20391 JORGE BRAVO DE RUEDA QUEROL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.564219</t>
+          <t>-11.559115</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.271073</t>
+          <t>-77.272031</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>356137</t>
+          <t>355958</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EL MUNDO DE LOS NIÑOS - MUNDO SCHOOL E.I.R.L.</t>
+          <t>20392 JUAN PASCUAL PRINGLES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.558917</t>
+          <t>-11.588432</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.270728</t>
+          <t>-77.260829</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>921</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>566098</t>
+          <t>355920</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA SOLEDAD</t>
+          <t>20390 HORTENCIA DULANTO DE LAS CASAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.579748</t>
+          <t>-11.56764</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.260341</t>
+          <t>-77.271648</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>734110</t>
+          <t>355864</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PEQUEÑA BELEN</t>
+          <t>20395 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.588477</t>
+          <t>-11.521612</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.259665</t>
+          <t>-77.248215</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>783332</t>
+          <t>355944</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>20799 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.559436</t>
+          <t>-11.490346</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.26912</t>
+          <t>-77.304839</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>863055</t>
+          <t>355779</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE CHANCAY</t>
+          <t>518 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.5647</t>
+          <t>-11.564071</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.27388</t>
+          <t>-77.26791</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>355963</t>
+          <t>863055</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CET 34</t>
+          <t>SANTO DOMINGO DE CHANCAY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.560798</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.268857</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>-11.5647</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-77.27388</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>-11.559436</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-77.26912</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>355816</t>
+          <t>734110</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20394 JORGE ORTIZ DUEÑAS</t>
+          <t>PEQUEÑA BELEN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.580878</t>
+          <t>493</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.268669</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-11.588477</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.259665</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>-11.579748</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-77.260341</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>356024</t>
+          <t>356137</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
+          <t>EL MUNDO DE LOS NIÑOS - MUNDO SCHOOL E.I.R.L.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.568961</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.27068</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>-11.558917</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.270728</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>734110</t>
+          <t>356081</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PEQUEÑA BELEN</t>
+          <t>VICENTE HONDARZA GOMEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.588477</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.259665</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>-11.564219</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.271073</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>863055</t>
+          <t>356024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE CHANCAY</t>
+          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.5647</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.27388</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-11.568961</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.27068</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>355802</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>85 MARIA INMACULADA CONCEPCION</t>
+          <t>20391 JORGE BRAVO DE RUEDA QUEROL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.566944</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.270559</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-11.559115</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.272031</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>356137</t>
+          <t>356000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EL MUNDO DE LOS NIÑOS - MUNDO SCHOOL E.I.R.L.</t>
+          <t>20393 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.558917</t>
+          <t>941</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.270728</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-11.50942</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.290471</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>356081</t>
+          <t>355982</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VICENTE HONDARZA GOMEZ</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.564219</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.271073</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-11.567256</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.271043</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-11.558853</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-77.273156</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>355982</t>
+          <t>355963</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>CET 34</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.567256</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.271043</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-11.560798</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.268857</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>355878</t>
+          <t>355958</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA CANDELARIA</t>
+          <t>20392 JUAN PASCUAL PRINGLES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.501327</t>
+          <t>921</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.295138</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>-11.588432</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.260829</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>356000</t>
+          <t>355944</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20393 TUPAC AMARU</t>
+          <t>20799 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.50942</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.290471</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>-11.490346</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.304839</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>356019</t>
+          <t>355920</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20391 JORGE BRAVO DE RUEDA QUEROL</t>
+          <t>20390 HORTENCIA DULANTO DE LAS CASAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.559115</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.272031</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>-11.56764</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.271648</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>355958</t>
+          <t>355878</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20392 JUAN PASCUAL PRINGLES</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.588432</t>
+          <t>854</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.260829</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>-11.501327</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.295138</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>355920</t>
+          <t>355864</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20390 HORTENCIA DULANTO DE LAS CASAS</t>
+          <t>20395 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.56764</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.271648</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>-11.521612</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.248215</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>355864</t>
+          <t>355816</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20395 NUESTRA SEÑORA DE FATIMA</t>
+          <t>20394 JORGE ORTIZ DUEÑAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.521612</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.248215</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>-11.580878</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.268669</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>355944</t>
+          <t>355802</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20799 DANIEL ALCIDES CARRION</t>
+          <t>85 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.490346</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.304839</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>-11.566944</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-77.270559</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>-11.564071</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-77.26791</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-CHANCAY.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
